--- a/tasks/finalpool/mrbeast-analysis/groundtruth_workspace/result.xlsx
+++ b/tasks/finalpool/mrbeast-analysis/groundtruth_workspace/result.xlsx
@@ -478,7 +478,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,13 +489,19 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -553,16 +559,16 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="21" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="21" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -574,8 +580,8 @@
     <xf xfId="0" numFmtId="21" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="21" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="21" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="21" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -919,7 +925,7 @@
       </c>
       <c r="H1" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -943,7 +949,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -967,7 +973,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -991,7 +997,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
       <c r="A5" s="3" t="s">
         <v>34</v>
       </c>
@@ -1008,14 +1014,14 @@
         <v>1044</v>
       </c>
       <c r="F5" s="5">
-        <v>1.0115972222222223</v>
+        <v>2.011111111111111</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
@@ -1039,7 +1045,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
       <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
@@ -1063,7 +1069,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
       <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
@@ -1087,7 +1093,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
       <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
@@ -1111,7 +1117,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
       <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
@@ -1135,7 +1141,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
       <c r="A11" s="3" t="s">
         <v>58</v>
       </c>
@@ -1159,7 +1165,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1183,7 +1189,7 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21.75">
       <c r="A13" s="3" t="s">
         <v>66</v>
       </c>
@@ -1207,7 +1213,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
       <c r="A14" s="3" t="s">
         <v>71</v>
       </c>
@@ -1231,7 +1237,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
       <c r="A15" s="3" t="s">
         <v>75</v>
       </c>
@@ -1255,7 +1261,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
       <c r="A16" s="3" t="s">
         <v>79</v>
       </c>
@@ -1725,7 +1731,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="5">
-        <v>1.0156944444444445</v>
+        <v>2.0152083333333333</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
